--- a/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-EX-MarkingFlag.xlsx
+++ b/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-EX-MarkingFlag.xlsx
@@ -1726,7 +1726,7 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>120</v>
@@ -2245,7 +2245,7 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>120</v>
@@ -2764,7 +2764,7 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>120</v>
@@ -2972,7 +2972,7 @@
         <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>120</v>
